--- a/data/trans_bre/P62-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P62-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,18; -25,87</t>
+          <t>-38,78; -25,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,05; -10,56</t>
+          <t>-23,72; -11,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,76; -8,32</t>
+          <t>-20,44; -7,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,83; -10,57</t>
+          <t>-26,36; -10,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-64,2; -49,43</t>
+          <t>-64,46; -49,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,88; -23,13</t>
+          <t>-45,37; -24,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,81; -19,98</t>
+          <t>-43,25; -18,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -20,34</t>
+          <t>-40,38; -19,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,98; -28,06</t>
+          <t>-40,18; -28,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -7,9</t>
+          <t>-18,01; -7,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,93; -12,04</t>
+          <t>-22,15; -11,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,56; -11,47</t>
+          <t>-25,5; -12,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,28; -53,5</t>
+          <t>-67,0; -54,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,65; -20,37</t>
+          <t>-41,73; -19,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-48,81; -28,83</t>
+          <t>-47,52; -27,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-45,0; -24,91</t>
+          <t>-44,27; -25,27</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-39,17; -24,55</t>
+          <t>-38,54; -24,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -6,12</t>
+          <t>-18,62; -5,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,18; -12,69</t>
+          <t>-25,69; -12,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 24,42</t>
+          <t>-24,66; 29,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,68; -45,32</t>
+          <t>-61,62; -45,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-43,61; -17,02</t>
+          <t>-44,03; -17,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-52,77; -29,68</t>
+          <t>-51,14; -28,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 50,58</t>
+          <t>-40,96; 54,67</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,55; -16,41</t>
+          <t>-28,15; -16,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,26; -11,26</t>
+          <t>-22,42; -11,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,57; -8,87</t>
+          <t>-20,32; -9,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,75; -3,54</t>
+          <t>-15,55; -3,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,31; -35,07</t>
+          <t>-53,55; -35,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,36; -25,25</t>
+          <t>-44,39; -25,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,54; -18,72</t>
+          <t>-37,81; -19,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,93; -7,91</t>
+          <t>-29,42; -7,01</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-32,9; -26,51</t>
+          <t>-32,83; -26,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,89; -12,06</t>
+          <t>-18,03; -12,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -13,08</t>
+          <t>-18,94; -13,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 7,24</t>
+          <t>-18,09; 4,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,44; -50,7</t>
+          <t>-58,31; -50,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,05; -28,52</t>
+          <t>-39,4; -28,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,92; -29,07</t>
+          <t>-39,55; -29,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 13,63</t>
+          <t>-32,63; 8,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P62-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P62-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-18,76</t>
+          <t>-21,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-31,38%</t>
+          <t>-34,29%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-38,78; -25,17</t>
+          <t>-39,21; -25,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -11,15</t>
+          <t>-24,5; -11,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,44; -7,39</t>
+          <t>-20,84; -7,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,36; -10,61</t>
+          <t>-27,67; -12,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-64,46; -49,48</t>
+          <t>-65,16; -49,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,37; -24,26</t>
+          <t>-46,62; -25,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,25; -18,2</t>
+          <t>-44,84; -19,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,38; -19,61</t>
+          <t>-42,03; -22,64</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-18,3</t>
+          <t>-19,52</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-35,32%</t>
+          <t>-36,99%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,18; -28,64</t>
+          <t>-39,74; -28,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,01; -7,66</t>
+          <t>-18,4; -8,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,15; -11,34</t>
+          <t>-22,02; -11,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-25,5; -12,06</t>
+          <t>-25,91; -13,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,0; -54,39</t>
+          <t>-66,74; -53,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,73; -19,99</t>
+          <t>-42,32; -21,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,52; -27,89</t>
+          <t>-47,56; -28,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,27; -25,27</t>
+          <t>-44,98; -26,78</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-24,77</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,04%</t>
+          <t>-41,44%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-38,54; -24,11</t>
+          <t>-38,91; -24,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,62; -5,89</t>
+          <t>-19,08; -6,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,69; -12,68</t>
+          <t>-25,79; -12,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 29,88</t>
+          <t>-32,01; -17,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,62; -45,73</t>
+          <t>-62,47; -45,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-44,03; -17,03</t>
+          <t>-44,52; -17,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,14; -28,87</t>
+          <t>-50,82; -27,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 54,67</t>
+          <t>-49,7; -32,44</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,83</t>
+          <t>-10,12</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-19,99%</t>
+          <t>-20,52%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,15; -16,18</t>
+          <t>-28,47; -16,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,42; -11,31</t>
+          <t>-22,53; -11,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,32; -9,29</t>
+          <t>-20,39; -8,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,55; -3,22</t>
+          <t>-16,14; -4,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,55; -35,5</t>
+          <t>-53,59; -36,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,39; -25,81</t>
+          <t>-45,12; -25,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,81; -19,26</t>
+          <t>-38,16; -18,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,42; -7,01</t>
+          <t>-30,67; -9,72</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-10,84</t>
+          <t>-18,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-20,03%</t>
+          <t>-33,17%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-32,83; -26,46</t>
+          <t>-32,87; -26,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,03; -12,27</t>
+          <t>-17,89; -11,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,94; -13,36</t>
+          <t>-19,13; -12,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 4,22</t>
+          <t>-21,47; -14,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,31; -50,77</t>
+          <t>-58,51; -50,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,4; -28,52</t>
+          <t>-39,21; -27,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -29,79</t>
+          <t>-39,94; -29,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 8,05</t>
+          <t>-37,45; -28,23</t>
         </is>
       </c>
     </row>
